--- a/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar30_Q4_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar30_Q4_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002252892750315151</v>
+        <v>0.002244759266350625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002252892750315151</v>
+        <v>0.002244759266350625</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001029415782901675</v>
+        <v>0.001071463135416891</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002214223652239152</v>
+        <v>0.002209041696227186</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002214223652239152</v>
+        <v>0.002209041696227186</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001071744268786122</v>
+        <v>0.001125417315723104</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.002218122391314001</v>
+        <v>0.002211691178544601</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002218122391314001</v>
+        <v>0.002211691178544601</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001034399253480323</v>
+        <v>0.001085324963220431</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00221556348687625</v>
+        <v>0.002206019821265477</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00221556348687625</v>
+        <v>0.002206019821265477</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001005381177125577</v>
+        <v>0.001046066182988644</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.002197424325566197</v>
+        <v>0.002183821275293679</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002197424325566197</v>
+        <v>0.002183821275293679</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009804630061708199</v>
+        <v>0.001008658176749059</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.002183593925470408</v>
+        <v>0.002165490763859764</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002183593925470408</v>
+        <v>0.002165490763859764</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000956511584953373</v>
+        <v>0.0009742312185909542</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.002158072704998805</v>
+        <v>0.002135128205625672</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002158072704998805</v>
+        <v>0.002135128205625672</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009341067733351657</v>
+        <v>0.000943986284016176</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.002130133128817777</v>
+        <v>0.00210226939634106</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002130133128817777</v>
+        <v>0.00210226939634106</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009135001015711847</v>
+        <v>0.0009181652755378961</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.002100384843722697</v>
+        <v>0.002067737975464618</v>
       </c>
       <c r="C10" t="n">
-        <v>0.002100384843722697</v>
+        <v>0.002067737975464618</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0008945517346637997</v>
+        <v>0.0008967103601415183</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002070173971853196</v>
+        <v>0.002033321739103605</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002070173971853196</v>
+        <v>0.002033321739103605</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0008765787465698894</v>
+        <v>0.0008791240223912956</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.002041217475018544</v>
+        <v>0.002000340009376749</v>
       </c>
       <c r="C12" t="n">
-        <v>0.002041217475018544</v>
+        <v>0.002000340009376749</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0008596835534592269</v>
+        <v>0.0008648528476986715</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.002014739943653362</v>
+        <v>0.001970651498640249</v>
       </c>
       <c r="C13" t="n">
-        <v>0.002014739943653362</v>
+        <v>0.001970651498640249</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0008447755556593085</v>
+        <v>0.0008529624521732282</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001991889186145116</v>
+        <v>0.001945278674196684</v>
       </c>
       <c r="C14" t="n">
-        <v>0.001991889186145116</v>
+        <v>0.001945278674196684</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0008299339819905601</v>
+        <v>0.0008423862007359286</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001973085951355452</v>
+        <v>0.001924641121540005</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001973085951355452</v>
+        <v>0.001924641121540005</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0008159862600347862</v>
+        <v>0.0008334097624167232</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001958553647885253</v>
+        <v>0.001908939226517722</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001958553647885253</v>
+        <v>0.001908939226517722</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0008036336709253201</v>
+        <v>0.0008257168465548034</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.001948628971480043</v>
+        <v>0.001898479991600073</v>
       </c>
       <c r="C17" t="n">
-        <v>0.001948628971480043</v>
+        <v>0.001898479991600073</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0007926892211601955</v>
+        <v>0.0008204259192499348</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.001943936756470342</v>
+        <v>0.001893859394484514</v>
       </c>
       <c r="C18" t="n">
-        <v>0.001943936756470342</v>
+        <v>0.001893859394484514</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0007833444521818952</v>
+        <v>0.0008173686270636085</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.001945249257192786</v>
+        <v>0.001895816224056997</v>
       </c>
       <c r="C19" t="n">
-        <v>0.001945249257192786</v>
+        <v>0.001895816224056997</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0007771629280099699</v>
+        <v>0.000818098594385475</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.001953332633855307</v>
+        <v>0.001905080512641905</v>
       </c>
       <c r="C20" t="n">
-        <v>0.001953332633855307</v>
+        <v>0.001905080512641905</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0007728243762883339</v>
+        <v>0.0008236852090691187</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.001968685444088784</v>
+        <v>0.001922088838128289</v>
       </c>
       <c r="C21" t="n">
-        <v>0.001968685444088784</v>
+        <v>0.001922088838128289</v>
       </c>
       <c r="D21" t="n">
-        <v>0.000772451134895843</v>
+        <v>0.0008345410344108661</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.001992057437430549</v>
+        <v>0.001947580725756298</v>
       </c>
       <c r="C22" t="n">
-        <v>0.001992057437430549</v>
+        <v>0.001947580725756298</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0007752504773398399</v>
+        <v>0.0008488888484981767</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.002023731447421569</v>
+        <v>0.001981797827685026</v>
       </c>
       <c r="C23" t="n">
-        <v>0.002023731447421569</v>
+        <v>0.001981797827685026</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00078094511570585</v>
+        <v>0.0008701152511724089</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.002064010981847481</v>
+        <v>0.0020200125923237</v>
       </c>
       <c r="C24" t="n">
-        <v>0.002064010981847481</v>
+        <v>0.0020200125923237</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0007922119280824948</v>
+        <v>0.0008946359348004708</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.002106805122987454</v>
+        <v>0.00207085579443649</v>
       </c>
       <c r="C25" t="n">
-        <v>0.002106805122987454</v>
+        <v>0.00207085579443649</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0008064817769477044</v>
+        <v>0.0009235555361476973</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.002164141511934399</v>
+        <v>0.002131731976800128</v>
       </c>
       <c r="C26" t="n">
-        <v>0.002164141511934399</v>
+        <v>0.002131731976800128</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0008226347742736304</v>
+        <v>0.000955709893011233</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.002231734462371366</v>
+        <v>0.002203036467067868</v>
       </c>
       <c r="C27" t="n">
-        <v>0.002231734462371366</v>
+        <v>0.002203036467067868</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0008410390683561997</v>
+        <v>0.0009900519134997919</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.002309918978756825</v>
+        <v>0.002285173032613334</v>
       </c>
       <c r="C28" t="n">
-        <v>0.002309918978756825</v>
+        <v>0.002285173032613334</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0008617990531472224</v>
+        <v>0.001025701194069927</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.002398997751608535</v>
+        <v>0.002378398928642547</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002398997751608535</v>
+        <v>0.002378398928642547</v>
       </c>
       <c r="D29" t="n">
-        <v>0.000882967374004901</v>
+        <v>0.001062580945098925</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.002499145255845924</v>
+        <v>0.002482872237495561</v>
       </c>
       <c r="C30" t="n">
-        <v>0.002499145255845924</v>
+        <v>0.002482872237495561</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0009050447001009588</v>
+        <v>0.001099487784527568</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.002610478948013484</v>
+        <v>0.002598681946845767</v>
       </c>
       <c r="C31" t="n">
-        <v>0.002610478948013484</v>
+        <v>0.002598681946845767</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0009271719754895862</v>
+        <v>0.001136293674052619</v>
       </c>
     </row>
   </sheetData>
